--- a/数据表/Entity/Weapon.xlsx
+++ b/数据表/Entity/Weapon.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -161,6 +161,12 @@
   </si>
   <si>
     <t>[SectorAngle:120]</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>[hitRadius:3]</t>
   </si>
 </sst>
 </file>
@@ -1100,8 +1106,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="5.81818181818182" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.4545454545455" style="1" customWidth="1"/>
@@ -1109,13 +1115,13 @@
     <col min="4" max="4" width="14.0909090909091" style="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.8181818181818" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="22.3636363636364" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.9090909090909" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5454545454545" customWidth="1"/>
+    <col min="9" max="9" width="22.5454545454545" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.0909090909091" style="1" customWidth="1"/>
     <col min="12" max="13" width="17.9090909090909" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="30.7272727272727" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.8181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1399,6 +1405,47 @@
         <v>43</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>204</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1">
+        <v>150</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="J8" s="1">
+        <v>80</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3</v>
+      </c>
+      <c r="L8" s="1">
+        <v>12</v>
+      </c>
+      <c r="M8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>40</v>
       </c>
     </row>

--- a/数据表/Entity/Weapon.xlsx
+++ b/数据表/Entity/Weapon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="21550" windowHeight="10080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -148,7 +148,7 @@
     <t>White</t>
   </si>
   <si>
-    <t>[hitRadius:2]</t>
+    <t>{"hitRadius":2}</t>
   </si>
   <si>
     <t>[]</t>
@@ -157,16 +157,19 @@
     <t>手枪</t>
   </si>
   <si>
+    <t>{}</t>
+  </si>
+  <si>
     <t>斧头</t>
   </si>
   <si>
-    <t>[SectorAngle:120]</t>
+    <t>{"SectorAngle":120}</t>
   </si>
   <si>
     <t>闪电</t>
   </si>
   <si>
-    <t>[hitRadius:3]</t>
+    <t>{"hitRadius":3}</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1364,7 @@
         <v>10000</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>40</v>
@@ -1375,7 +1378,7 @@
         <v>203</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>37</v>
@@ -1402,7 +1405,7 @@
         <v>10000</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>40</v>
@@ -1416,7 +1419,7 @@
         <v>204</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>37</v>
@@ -1443,7 +1446,7 @@
         <v>10000</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>40</v>

--- a/数据表/Entity/Weapon.xlsx
+++ b/数据表/Entity/Weapon.xlsx
@@ -29,17 +29,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>武器表</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
+    <t>列1</t>
+  </si>
+  <si>
     <t>EntityTypeId</t>
   </si>
   <si>
@@ -94,52 +94,180 @@
     <t>StatModifier[]</t>
   </si>
   <si>
-    <t>武器编号</t>
-  </si>
-  <si>
-    <t>策划备注</t>
-  </si>
-  <si>
-    <t>武器实体编号</t>
-  </si>
-  <si>
-    <t>武器名</t>
-  </si>
-  <si>
-    <t>图标资源名</t>
-  </si>
-  <si>
-    <t>道具品质</t>
-  </si>
-  <si>
-    <t>武器价格</t>
-  </si>
-  <si>
-    <t>价格浮动</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>范围</t>
-  </si>
-  <si>
-    <t>攻击音效编号</t>
-  </si>
-  <si>
-    <t>额外参数</t>
-  </si>
-  <si>
-    <t>额外属性</t>
-  </si>
-  <si>
-    <t>玩家武器</t>
-  </si>
-  <si>
-    <t>小刀</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>策划备注</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器实体编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具品质</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器价格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>价格浮动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冷却</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>范围</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击音效编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>额外参数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>额外属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家武器</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小刀</t>
+    </r>
   </si>
   <si>
     <t>Almighty_Icon</t>
@@ -154,22 +282,60 @@
     <t>[]</t>
   </si>
   <si>
-    <t>手枪</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手枪</t>
+    </r>
   </si>
   <si>
     <t>{}</t>
   </si>
   <si>
-    <t>斧头</t>
-  </si>
-  <si>
-    <t>{"SectorAngle":120}</t>
-  </si>
-  <si>
-    <t>闪电</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>斧头</t>
+    </r>
+  </si>
+  <si>
+    <t>{"sectorAngle":120}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闪电</t>
+    </r>
   </si>
   <si>
     <t>{"hitRadius":3}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长枪</t>
+    </r>
+  </si>
+  <si>
+    <t>{"hitRadius":0.3,"thrustDistance":1.2,"pierceLength":0.3}</t>
   </si>
 </sst>
 </file>
@@ -182,13 +348,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -333,6 +505,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -655,147 +833,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,6 +1040,138 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Consolas"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -857,6 +1179,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:O8" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O8" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="#" dataDxfId="0"/>
+    <tableColumn id="2" name="Id" dataDxfId="1"/>
+    <tableColumn id="3" name="列1" dataDxfId="2"/>
+    <tableColumn id="4" name="EntityTypeId" dataDxfId="3"/>
+    <tableColumn id="5" name="Title" dataDxfId="4"/>
+    <tableColumn id="6" name="IconAssetName" dataDxfId="5"/>
+    <tableColumn id="7" name="Rarity" dataDxfId="6"/>
+    <tableColumn id="8" name="Price" dataDxfId="7"/>
+    <tableColumn id="9" name="PriceRandomPercent" dataDxfId="8"/>
+    <tableColumn id="10" name="Attack" dataDxfId="9"/>
+    <tableColumn id="11" name="Cooldown" dataDxfId="10"/>
+    <tableColumn id="12" name="AttackRange" dataDxfId="11"/>
+    <tableColumn id="13" name="AttackSoundId" dataDxfId="12"/>
+    <tableColumn id="14" name="Pramas" dataDxfId="13"/>
+    <tableColumn id="15" name="Modifiers"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,7 +1456,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="5.81818181818182" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.4545454545455" style="1" customWidth="1"/>
@@ -1124,338 +1470,363 @@
     <col min="10" max="10" width="10.6363636363636" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.0909090909091" style="1" customWidth="1"/>
     <col min="12" max="13" width="17.9090909090909" style="1" customWidth="1"/>
-    <col min="14" max="14" width="30.7272727272727" style="1" customWidth="1"/>
+    <col min="14" max="14" width="49.7272727272727" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.8181818181818" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>14</v>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:15">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4">
+        <v>201</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="7">
+        <v>120</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J4" s="4">
+        <v>100</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:15">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>202</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="7">
+        <v>130</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J5" s="1">
+        <v>120</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
         <v>15</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>20</v>
+      <c r="M5" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>34</v>
+    <row r="6" ht="30" customHeight="1" spans="1:15">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>203</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>150</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>5</v>
+      </c>
+      <c r="M6" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2">
-        <v>201</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1" t="s">
+    <row r="7" ht="30" customHeight="1" spans="1:15">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1">
+        <v>204</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3">
-        <v>120</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="H7" s="1">
+        <v>150</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="J7" s="1">
+        <v>80</v>
+      </c>
+      <c r="K7" s="1">
+        <v>3</v>
+      </c>
+      <c r="L7" s="1">
+        <v>12</v>
+      </c>
+      <c r="M7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:15">
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>205</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1">
         <v>100</v>
       </c>
-      <c r="K5" s="2">
+      <c r="I8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>100</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.5</v>
       </c>
-      <c r="L5" s="2">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>202</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="3">
-        <v>130</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="J6" s="1">
-        <v>120</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>15</v>
-      </c>
-      <c r="M6" s="2">
-        <v>10000</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>203</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="1">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>150</v>
-      </c>
-      <c r="K7" s="1">
-        <v>2</v>
-      </c>
-      <c r="L7" s="1">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2">
-        <v>10000</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>204</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="1">
-        <v>150</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="J8" s="1">
-        <v>80</v>
-      </c>
-      <c r="K8" s="1">
-        <v>3</v>
-      </c>
       <c r="L8" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M8" s="1">
         <v>10000</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>40</v>
+      <c r="N8" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/数据表/Entity/Weapon.xlsx
+++ b/数据表/Entity/Weapon.xlsx
@@ -335,7 +335,7 @@
     </r>
   </si>
   <si>
-    <t>{"hitRadius":0.3,"thrustDistance":1.2,"pierceLength":0.3}</t>
+    <t>{"hitHalfWidth":0.7,"pierceLength":4.5,"hitHeight":0.5,"hitCenterYOffset":0}</t>
   </si>
 </sst>
 </file>
@@ -963,7 +963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -975,15 +975,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1040,7 +1031,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <font>
         <name val="Consolas"/>
@@ -1171,6 +1162,9 @@
       </font>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1199,7 +1193,7 @@
     <tableColumn id="12" name="AttackRange" dataDxfId="11"/>
     <tableColumn id="13" name="AttackSoundId" dataDxfId="12"/>
     <tableColumn id="14" name="Pramas" dataDxfId="13"/>
-    <tableColumn id="15" name="Modifiers"/>
+    <tableColumn id="15" name="Modifiers" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1482,7 +1476,7 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -1515,10 +1509,10 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1529,7 +1523,7 @@
       <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
@@ -1560,10 +1554,10 @@
       <c r="M2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1607,55 +1601,55 @@
       <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:15">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>201</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="4">
         <v>120</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="4">
         <v>0.05</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>100</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>1.5</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>5</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="3">
         <v>10000</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1666,19 +1660,19 @@
       <c r="D5" s="1">
         <v>202</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="4">
         <v>130</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="4">
         <v>0.05</v>
       </c>
       <c r="J5" s="1">
@@ -1690,13 +1684,13 @@
       <c r="L5" s="1">
         <v>15</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>10000</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1707,19 +1701,19 @@
       <c r="D6" s="1">
         <v>203</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="1">
         <v>100</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="4">
         <v>0.1</v>
       </c>
       <c r="J6" s="1">
@@ -1731,13 +1725,13 @@
       <c r="L6" s="1">
         <v>5</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="3">
         <v>10000</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="N6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1748,13 +1742,13 @@
       <c r="D7" s="1">
         <v>204</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="1">
@@ -1775,10 +1769,10 @@
       <c r="M7" s="1">
         <v>10000</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1789,13 +1783,13 @@
       <c r="D8" s="1">
         <v>205</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="1">
@@ -1811,12 +1805,12 @@
         <v>1.5</v>
       </c>
       <c r="L8" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1">
         <v>10000</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="4" t="s">
         <v>48</v>
       </c>
     </row>
